--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487097_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487097_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6506</v>
+        <v>10.7602</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4857</v>
+        <v>6.8631</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1648</v>
+        <v>3.8971</v>
       </c>
       <c r="G2" t="n">
         <v>7.735</v>
@@ -610,13 +610,13 @@
         <v>3.0881</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5295</v>
+        <v>0.6392</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2136</v>
+        <v>0.591</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3159</v>
+        <v>0.0482</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3431</v>
+        <v>5.5028</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2192</v>
+        <v>1.3789</v>
       </c>
       <c r="F3" t="n">
         <v>4.1239</v>
@@ -688,10 +688,10 @@
         <v>2.5091</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1494</v>
+        <v>0.309</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0172</v>
+        <v>0.1425</v>
       </c>
       <c r="U3" t="n">
         <v>0.1665</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5615</v>
+        <v>4.2823</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6106</v>
+        <v>3.1708</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9509</v>
+        <v>1.1116</v>
       </c>
       <c r="G4" t="n">
         <v>6.0783</v>
@@ -766,13 +766,13 @@
         <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8376</v>
+        <v>-1.1167</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7588</v>
+        <v>-0.1986</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0788</v>
+        <v>-0.9181</v>
       </c>
       <c r="V4" t="n">
         <v>0.2859</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.339</v>
+        <v>3.4906</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4733</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8657</v>
+        <v>2.8389</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0435</v>
@@ -844,13 +844,13 @@
         <v>2.7021</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4475</v>
+        <v>-0.2958</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0026</v>
+        <v>0.1759</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4449</v>
+        <v>-0.4717</v>
       </c>
       <c r="V5" t="n">
         <v>2.1278</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0004</v>
+        <v>3.2542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.698</v>
+        <v>0.6574</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3024</v>
+        <v>2.5968</v>
       </c>
       <c r="G6" t="n">
         <v>3.2393</v>
@@ -922,13 +922,13 @@
         <v>2.5091</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5321</v>
+        <v>-0.2783</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2499</v>
+        <v>0.2092</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.782</v>
+        <v>-0.4875</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2859</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.491</v>
+        <v>2.1712</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6886</v>
+        <v>-1.169</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1796</v>
+        <v>3.3402</v>
       </c>
       <c r="G7" t="n">
         <v>5.0557</v>
@@ -1000,13 +1000,13 @@
         <v>2.7021</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8276</v>
+        <v>-0.1474</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4772</v>
+        <v>0.0423</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3504</v>
+        <v>-0.1897</v>
       </c>
       <c r="V7" t="n">
         <v>-0.614</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7264</v>
+        <v>0.9465</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8803</v>
+        <v>-0.8208</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6068</v>
+        <v>1.7674</v>
       </c>
       <c r="G8" t="n">
         <v>1.2724</v>
@@ -1078,13 +1078,13 @@
         <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.16</v>
+        <v>0.0601</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0595</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1005</v>
+        <v>0.0601</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-1.2711</v>
       </c>
       <c r="E9" t="n">
         <v>0.4242</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2402</v>
+        <v>-1.6953</v>
       </c>
       <c r="G9" t="n">
         <v>1.4546</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3008</v>
+        <v>-0.7559</v>
       </c>
       <c r="T9" t="n">
         <v>-0.4164</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1156</v>
+        <v>-0.3394</v>
       </c>
       <c r="V9" t="n">
         <v>-2.7418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2533</v>
+        <v>-2.4199</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0267</v>
+        <v>-4.3271</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7734</v>
+        <v>1.9072</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6393</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2822</v>
+        <v>-0.4488</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2062</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4885</v>
+        <v>-0.3546</v>
       </c>
       <c r="V10" t="n">
         <v>2.2123</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4687</v>
+        <v>-2.55</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2827</v>
+        <v>-1.123</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.186</v>
+        <v>-1.427</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0424</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8124</v>
+        <v>-0.8937</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4759</v>
+        <v>-0.3163</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3365</v>
+        <v>-0.5774</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6697</v>
+        <v>-5.3702</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.949</v>
+        <v>-5.7298</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2793</v>
+        <v>0.3596</v>
       </c>
       <c r="G12" t="n">
         <v>-4.623</v>
@@ -1390,13 +1390,13 @@
         <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2975</v>
+        <v>-0.9981</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4468</v>
+        <v>-0.2277</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8507</v>
+        <v>-0.7704</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3281</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.90430000000001</v>
+        <v>18.7966</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.9162999999999997</v>
+        <v>-0.02360000000000007</v>
       </c>
       <c r="F13" t="n">
-        <v>18.8206</v>
+        <v>18.8204</v>
       </c>
       <c r="G13" t="n">
         <v>15.816</v>
@@ -1468,13 +1468,13 @@
         <v>20.2658</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8188</v>
+        <v>-3.9264</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9847000000000002</v>
+        <v>-0.09230000000000022</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.834300000000001</v>
+        <v>-3.834</v>
       </c>
       <c r="V13" t="n">
         <v>4.012</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2286</v>
+        <v>1.3475</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1559</v>
+        <v>1.9542</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9273</v>
+        <v>-0.6067</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3408</v>
@@ -1546,13 +1546,13 @@
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0676</v>
+        <v>1.1865</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2818</v>
+        <v>1.0801</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2142</v>
+        <v>0.1064</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6562</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3586</v>
+        <v>1.2337</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3795</v>
+        <v>0.8802</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0209</v>
+        <v>0.3536</v>
       </c>
       <c r="G15" t="n">
         <v>0.3212</v>
@@ -1624,13 +1624,13 @@
         <v>0.965</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6418</v>
+        <v>0.2333</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4019</v>
+        <v>0.0988</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2399</v>
+        <v>0.1345</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2859</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3121</v>
+        <v>0.5989</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3106</v>
+        <v>-2.2104</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6226</v>
+        <v>2.8093</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1878</v>
@@ -1702,13 +1702,13 @@
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6736</v>
+        <v>0.9604</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3239</v>
+        <v>0.4241</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3496</v>
+        <v>0.5364</v>
       </c>
       <c r="V16" t="n">
         <v>1.5983</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GOMEZ MERODIO</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0746</v>
+        <v>0.343</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1785</v>
+        <v>-1.3192</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2531</v>
+        <v>1.6622</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1936</v>
+        <v>0.1692</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>0.9553</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1335</v>
+        <v>-0.7861</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.1635</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.7904</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.6269</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1936</v>
+        <v>-0.9943</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06</v>
+        <v>-0.835</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1335</v>
+        <v>-0.1592</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3161</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.119</v>
+        <v>0.7529</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1785</v>
+        <v>0.1266</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0595</v>
+        <v>0.6263</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>J. GOMEZ MERODIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4447</v>
+        <v>0.0746</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.097</v>
+        <v>-0.1785</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6523</v>
+        <v>0.2531</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8992</v>
+        <v>0.1936</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8589</v>
+        <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0403</v>
+        <v>0.1335</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6723</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3778</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2945</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2269</v>
+        <v>0.1936</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4811</v>
+        <v>0.06</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2542</v>
+        <v>0.1335</v>
       </c>
       <c r="P18" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1231</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9756</v>
+        <v>-0.119</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9915</v>
+        <v>-0.1785</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0159</v>
+        <v>0.0595</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.172</v>
+        <v>-0.2041</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.621</v>
+        <v>-1.4976</v>
       </c>
       <c r="F19" t="n">
-        <v>1.449</v>
+        <v>1.2935</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1692</v>
+        <v>-1.8992</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9553</v>
+        <v>-0.8589</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7861</v>
+        <v>-1.0403</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1635</v>
+        <v>-1.6723</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7904</v>
+        <v>-0.3778</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6269</v>
+        <v>-1.2945</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9943</v>
+        <v>-0.2269</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.835</v>
+        <v>-0.4811</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1592</v>
+        <v>0.2542</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.579</v>
+        <v>0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7621</v>
+        <v>1.2162</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1752</v>
+        <v>0.591</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4131</v>
+        <v>0.6253</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0826</v>
+        <v>-1.9352</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4523</v>
+        <v>-2.6525</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3697</v>
+        <v>0.7173</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1385</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.735</v>
+        <v>0.8824</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6954</v>
+        <v>0.4951</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0396</v>
+        <v>0.3873</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3281</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.04</v>
+        <v>-3.7868</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.985</v>
+        <v>-4.7847</v>
       </c>
       <c r="F21" t="n">
-        <v>0.945</v>
+        <v>0.9979</v>
       </c>
       <c r="G21" t="n">
         <v>-4.4501</v>
@@ -2092,13 +2092,13 @@
         <v>2.3161</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7033</v>
+        <v>0.9565</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1455</v>
+        <v>0.3457</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5578</v>
+        <v>0.6107</v>
       </c>
       <c r="V21" t="n">
         <v>0.2859</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4657</v>
+        <v>-5.6591</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5461</v>
+        <v>-2.2471</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9196</v>
+        <v>-3.412</v>
       </c>
       <c r="G22" t="n">
         <v>-2.881</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2572</v>
+        <v>1.0639</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5401</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2829</v>
+        <v>0.2247</v>
       </c>
       <c r="V22" t="n">
         <v>-3.0699</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6732</v>
+        <v>-7.2465</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.1654</v>
+        <v>-6.7648</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5078</v>
+        <v>-0.4817</v>
       </c>
       <c r="G23" t="n">
         <v>-4.6024</v>
@@ -2248,13 +2248,13 @@
         <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0707</v>
+        <v>0.3559</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3886</v>
+        <v>0.0119</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3179</v>
+        <v>0.344</v>
       </c>
       <c r="V23" t="n">
         <v>-1.842</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.9043</v>
+        <v>-15.234</v>
       </c>
       <c r="E24" t="n">
-        <v>-18.8205</v>
+        <v>-18.8204</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9161000000000006</v>
+        <v>3.5865</v>
       </c>
       <c r="G24" t="n">
         <v>-15.8158</v>
@@ -2311,7 +2311,7 @@
         <v>-8.642100000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.7815</v>
+        <v>-7.781499999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-0.8605</v>
@@ -2326,13 +2326,13 @@
         <v>17.3708</v>
       </c>
       <c r="S24" t="n">
-        <v>4.8187</v>
+        <v>7.489000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>3.834</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9846000000000001</v>
+        <v>3.6551</v>
       </c>
       <c r="V24" t="n">
         <v>-4.012</v>
@@ -2341,7 +2341,7 @@
         <v>4.7852</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.7974</v>
+        <v>-8.797400000000001</v>
       </c>
     </row>
   </sheetData>
